--- a/SQExcel.Portal/src/content/docs/ja/docs/images/large-scale/large-scale.xlsx
+++ b/SQExcel.Portal/src/content/docs/ja/docs/images/large-scale/large-scale.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos_MS\East\SQL2Excel\v100\SQL2Excel\SQL2Excel.Help\src\content\docs\ja\images\large-scale\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos_GitEms\sqexcel\SQExcel.Portal\src\content\docs\ja\docs\images\large-scale\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A8086A9-3AC4-4392-A884-24C98AC3F654}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBAE9998-E717-4A44-842C-7FC9B4872222}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1140" yWindow="1140" windowWidth="24540" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2280" yWindow="0" windowWidth="19280" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LARGE_SCALE" sheetId="5" r:id="rId1"/>
@@ -2166,1997 +2166,6 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>46</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>72339</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BF017EE5-B97F-3076-DB92-D24445B2C55B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="234950" y="1143000"/>
-          <a:ext cx="10801350" cy="7844739"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>226785</xdr:colOff>
-      <xdr:row>129</xdr:row>
-      <xdr:rowOff>27215</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>38</xdr:col>
-      <xdr:colOff>173808</xdr:colOff>
-      <xdr:row>150</xdr:row>
-      <xdr:rowOff>57163</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="30" name="グループ化 29">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F6C50B54-12E5-EAC0-A0F4-7BB9D491C809}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="458373" y="29902097"/>
-          <a:ext cx="8515788" cy="4893301"/>
-          <a:chOff x="469900" y="28647572"/>
-          <a:chExt cx="8641080" cy="4830548"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="29" name="図 28">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7F9142CE-7E89-2A9A-A46E-8D7835D7ADF8}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="469900" y="28647572"/>
-            <a:ext cx="8641080" cy="4830548"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-      </xdr:pic>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="6" name="正方形/長方形 5">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D80B9066-FBD9-44C5-85D2-CD32E326E1B9}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="612347" y="32618136"/>
-            <a:ext cx="3553958" cy="258012"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="10" name="正方形/長方形 9">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DEE2C7AD-4FE5-6E6F-45D0-AD49149A9DD0}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="5295966" y="31881122"/>
-            <a:ext cx="2674225" cy="832125"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>226785</xdr:colOff>
-      <xdr:row>156</xdr:row>
-      <xdr:rowOff>18143</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>47</xdr:col>
-      <xdr:colOff>223797</xdr:colOff>
-      <xdr:row>199</xdr:row>
-      <xdr:rowOff>71593</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="4" name="グループ化 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E23210DE-EE71-0266-E784-864445BD622B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="458373" y="36145908"/>
-          <a:ext cx="10650071" cy="10011744"/>
-          <a:chOff x="461735" y="35679743"/>
-          <a:chExt cx="10804712" cy="9883250"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:grpSp>
-        <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="20" name="グループ化 19">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A1DF8CDD-7427-FFCA-3E88-F832DEB0588D}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvGrpSpPr/>
-        </xdr:nvGrpSpPr>
-        <xdr:grpSpPr>
-          <a:xfrm>
-            <a:off x="461735" y="35679743"/>
-            <a:ext cx="10800443" cy="4848180"/>
-            <a:chOff x="469900" y="31318200"/>
-            <a:chExt cx="10801350" cy="4848180"/>
-          </a:xfrm>
-        </xdr:grpSpPr>
-        <xdr:pic>
-          <xdr:nvPicPr>
-            <xdr:cNvPr id="15" name="図 14">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4BC7F28C-E706-A061-0DD2-0D51A2323C1E}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvPicPr>
-              <a:picLocks noChangeAspect="1"/>
-            </xdr:cNvPicPr>
-          </xdr:nvPicPr>
-          <xdr:blipFill>
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-            <a:stretch>
-              <a:fillRect/>
-            </a:stretch>
-          </xdr:blipFill>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="469900" y="31318200"/>
-              <a:ext cx="10801350" cy="4848180"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-          </xdr:spPr>
-        </xdr:pic>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="16" name="正方形/長方形 15">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{99B056D6-F636-48D8-8E18-6030070FD15D}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="1667062" y="34049447"/>
-              <a:ext cx="9435353" cy="1405965"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln w="19050">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="2">
-              <a:schemeClr val="accent1">
-                <a:shade val="15000"/>
-              </a:schemeClr>
-            </a:lnRef>
-            <a:fillRef idx="1">
-              <a:schemeClr val="accent1"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:schemeClr val="accent1"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="lt1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-              <a:prstTxWarp prst="textNoShape">
-                <a:avLst/>
-              </a:prstTxWarp>
-              <a:noAutofit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </xdr:grpSp>
-      <xdr:grpSp>
-        <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="19" name="グループ化 18">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{685B3851-9BB5-3E8A-FE75-B0460732DAE0}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvGrpSpPr/>
-        </xdr:nvGrpSpPr>
-        <xdr:grpSpPr>
-          <a:xfrm>
-            <a:off x="461735" y="40714814"/>
-            <a:ext cx="10804712" cy="4848179"/>
-            <a:chOff x="469900" y="36576000"/>
-            <a:chExt cx="10801350" cy="4848180"/>
-          </a:xfrm>
-        </xdr:grpSpPr>
-        <xdr:pic>
-          <xdr:nvPicPr>
-            <xdr:cNvPr id="17" name="図 16">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C19CE300-BC63-35F7-C7D7-2EAD130389D9}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvPicPr>
-              <a:picLocks noChangeAspect="1"/>
-            </xdr:cNvPicPr>
-          </xdr:nvPicPr>
-          <xdr:blipFill>
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-            <a:stretch>
-              <a:fillRect/>
-            </a:stretch>
-          </xdr:blipFill>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="469900" y="36576000"/>
-              <a:ext cx="10801350" cy="4848180"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-          </xdr:spPr>
-        </xdr:pic>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="18" name="正方形/長方形 17">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F903AE1-B6F0-4384-A5C7-C216727251B8}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="1652120" y="39334142"/>
-              <a:ext cx="9435353" cy="1408952"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln w="19050">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="2">
-              <a:schemeClr val="accent1">
-                <a:shade val="15000"/>
-              </a:schemeClr>
-            </a:lnRef>
-            <a:fillRef idx="1">
-              <a:schemeClr val="accent1"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:schemeClr val="accent1"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="lt1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-              <a:prstTxWarp prst="textNoShape">
-                <a:avLst/>
-              </a:prstTxWarp>
-              <a:noAutofit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </xdr:grpSp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>87</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>48</xdr:col>
-      <xdr:colOff>4482</xdr:colOff>
-      <xdr:row>120</xdr:row>
-      <xdr:rowOff>63948</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="28" name="グループ化 27">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E22C8FD6-F62C-B794-452E-D1BFD4FC1830}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="463176" y="20148176"/>
-          <a:ext cx="10657541" cy="7706360"/>
-          <a:chOff x="469900" y="19659600"/>
-          <a:chExt cx="10812182" cy="7607748"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:grpSp>
-        <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="26" name="グループ化 25">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AEBCB02B-1EB2-0D46-734B-5FDBF27841FC}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvGrpSpPr/>
-        </xdr:nvGrpSpPr>
-        <xdr:grpSpPr>
-          <a:xfrm>
-            <a:off x="469900" y="19659600"/>
-            <a:ext cx="10801350" cy="3631672"/>
-            <a:chOff x="469900" y="24231600"/>
-            <a:chExt cx="10801350" cy="3631673"/>
-          </a:xfrm>
-        </xdr:grpSpPr>
-        <xdr:pic>
-          <xdr:nvPicPr>
-            <xdr:cNvPr id="22" name="図 21">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{58677F60-D64E-96C7-5976-08643B1BE810}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvPicPr>
-              <a:picLocks noChangeAspect="1"/>
-            </xdr:cNvPicPr>
-          </xdr:nvPicPr>
-          <xdr:blipFill>
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-            <a:stretch>
-              <a:fillRect/>
-            </a:stretch>
-          </xdr:blipFill>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="469900" y="24231600"/>
-              <a:ext cx="10801350" cy="3631673"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-          </xdr:spPr>
-        </xdr:pic>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="14" name="正方形/長方形 13">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C15181F7-3FF8-439F-B980-ECADE959571F}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="1756708" y="25591247"/>
-              <a:ext cx="1409701" cy="1274482"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln w="19050">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="2">
-              <a:schemeClr val="accent1">
-                <a:shade val="15000"/>
-              </a:schemeClr>
-            </a:lnRef>
-            <a:fillRef idx="1">
-              <a:schemeClr val="accent1"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:schemeClr val="accent1"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="lt1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-              <a:prstTxWarp prst="textNoShape">
-                <a:avLst/>
-              </a:prstTxWarp>
-              <a:noAutofit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="23" name="正方形/長方形 22">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E279C728-F6A2-4081-9D5F-E782D2AA1805}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="611841" y="26517600"/>
-              <a:ext cx="850154" cy="340658"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln w="19050">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="2">
-              <a:schemeClr val="accent1">
-                <a:shade val="15000"/>
-              </a:schemeClr>
-            </a:lnRef>
-            <a:fillRef idx="1">
-              <a:schemeClr val="accent1"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:schemeClr val="accent1"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="lt1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-              <a:prstTxWarp prst="textNoShape">
-                <a:avLst/>
-              </a:prstTxWarp>
-              <a:noAutofit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </xdr:grpSp>
-      <xdr:grpSp>
-        <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="27" name="グループ化 26">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DAFB44ED-67DE-E8E2-A8B0-B9163D3A8CDC}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvGrpSpPr/>
-        </xdr:nvGrpSpPr>
-        <xdr:grpSpPr>
-          <a:xfrm>
-            <a:off x="477370" y="23481554"/>
-            <a:ext cx="10804712" cy="3785794"/>
-            <a:chOff x="477370" y="28053554"/>
-            <a:chExt cx="10804712" cy="3785794"/>
-          </a:xfrm>
-        </xdr:grpSpPr>
-        <xdr:pic>
-          <xdr:nvPicPr>
-            <xdr:cNvPr id="21" name="図 20">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E49F11E9-615B-0003-A94F-A557E2E579B2}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvPicPr>
-              <a:picLocks noChangeAspect="1"/>
-            </xdr:cNvPicPr>
-          </xdr:nvPicPr>
-          <xdr:blipFill>
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-            <a:stretch>
-              <a:fillRect/>
-            </a:stretch>
-          </xdr:blipFill>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="477370" y="28053554"/>
-              <a:ext cx="10804712" cy="3785794"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-          </xdr:spPr>
-        </xdr:pic>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="24" name="正方形/長方形 23">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5E4BEC83-F88E-4F71-BF7F-BA6DEADB2F35}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="3233643" y="29440094"/>
-              <a:ext cx="1159810" cy="1371600"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln w="19050">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="2">
-              <a:schemeClr val="accent1">
-                <a:shade val="15000"/>
-              </a:schemeClr>
-            </a:lnRef>
-            <a:fillRef idx="1">
-              <a:schemeClr val="accent1"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:schemeClr val="accent1"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="lt1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-              <a:prstTxWarp prst="textNoShape">
-                <a:avLst/>
-              </a:prstTxWarp>
-              <a:noAutofit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="25" name="正方形/長方形 24">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C21E088F-C003-492C-BC9A-D4F95436DB52}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="704850" y="30361965"/>
-              <a:ext cx="846793" cy="337670"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln w="19050">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="2">
-              <a:schemeClr val="accent1">
-                <a:shade val="15000"/>
-              </a:schemeClr>
-            </a:lnRef>
-            <a:fillRef idx="1">
-              <a:schemeClr val="accent1"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:schemeClr val="accent1"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="lt1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-              <a:prstTxWarp prst="textNoShape">
-                <a:avLst/>
-              </a:prstTxWarp>
-              <a:noAutofit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </xdr:grpSp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>10139</xdr:colOff>
-      <xdr:row>252</xdr:row>
-      <xdr:rowOff>195835</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>48</xdr:col>
-      <xdr:colOff>2882</xdr:colOff>
-      <xdr:row>291</xdr:row>
-      <xdr:rowOff>53241</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="46" name="グループ化 45">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8842D565-9281-EE18-CAFA-88240E689EAB}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="473315" y="58556070"/>
-          <a:ext cx="10645802" cy="8889347"/>
-          <a:chOff x="469900" y="56464200"/>
-          <a:chExt cx="10801350" cy="8775793"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:grpSp>
-        <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="39" name="グループ化 38">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{86ED658B-30DD-AF28-1045-B5E23B9C9DD4}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvGrpSpPr/>
-        </xdr:nvGrpSpPr>
-        <xdr:grpSpPr>
-          <a:xfrm>
-            <a:off x="1098550" y="60803117"/>
-            <a:ext cx="8708263" cy="4436876"/>
-            <a:chOff x="628650" y="61264800"/>
-            <a:chExt cx="8708262" cy="4439864"/>
-          </a:xfrm>
-        </xdr:grpSpPr>
-        <xdr:pic>
-          <xdr:nvPicPr>
-            <xdr:cNvPr id="35" name="図 34">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0AE4A581-2C8F-F989-CA65-1EAFBC27C359}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvPicPr>
-              <a:picLocks noChangeAspect="1"/>
-            </xdr:cNvPicPr>
-          </xdr:nvPicPr>
-          <xdr:blipFill>
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-            <a:stretch>
-              <a:fillRect/>
-            </a:stretch>
-          </xdr:blipFill>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="695832" y="61264800"/>
-              <a:ext cx="8641080" cy="4439864"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-          </xdr:spPr>
-        </xdr:pic>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="32" name="正方形/長方形 31">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{408A2820-2DB6-4AA8-88B4-D47DD642983F}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="628650" y="63303150"/>
-              <a:ext cx="7334250" cy="184150"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln w="19050">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="2">
-              <a:schemeClr val="accent1">
-                <a:shade val="15000"/>
-              </a:schemeClr>
-            </a:lnRef>
-            <a:fillRef idx="1">
-              <a:schemeClr val="accent1"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:schemeClr val="accent1"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="lt1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-              <a:prstTxWarp prst="textNoShape">
-                <a:avLst/>
-              </a:prstTxWarp>
-              <a:noAutofit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="33" name="正方形/長方形 32">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{55C9EF02-38AC-49EA-B3E7-6574CCEFF4B5}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="7956550" y="62591950"/>
-              <a:ext cx="1143000" cy="2470150"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln w="19050">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="2">
-              <a:schemeClr val="accent1">
-                <a:shade val="15000"/>
-              </a:schemeClr>
-            </a:lnRef>
-            <a:fillRef idx="1">
-              <a:schemeClr val="accent1"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:schemeClr val="accent1"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="lt1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-              <a:prstTxWarp prst="textNoShape">
-                <a:avLst/>
-              </a:prstTxWarp>
-              <a:noAutofit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </xdr:grpSp>
-      <xdr:grpSp>
-        <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="38" name="グループ化 37">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D139E68B-8315-CF5B-0C07-8E4B748BFBA5}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvGrpSpPr/>
-        </xdr:nvGrpSpPr>
-        <xdr:grpSpPr>
-          <a:xfrm>
-            <a:off x="469900" y="56464200"/>
-            <a:ext cx="10801350" cy="4078861"/>
-            <a:chOff x="469900" y="56921400"/>
-            <a:chExt cx="10801350" cy="4078861"/>
-          </a:xfrm>
-        </xdr:grpSpPr>
-        <xdr:pic>
-          <xdr:nvPicPr>
-            <xdr:cNvPr id="8" name="図 7">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3BD021D8-7293-67D3-F400-8BCFE7E6B04F}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvPicPr>
-              <a:picLocks noChangeAspect="1"/>
-            </xdr:cNvPicPr>
-          </xdr:nvPicPr>
-          <xdr:blipFill>
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-            <a:stretch>
-              <a:fillRect/>
-            </a:stretch>
-          </xdr:blipFill>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="469900" y="56921400"/>
-              <a:ext cx="10801350" cy="4078861"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-          </xdr:spPr>
-        </xdr:pic>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="36" name="正方形/長方形 35">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D8EF5C6-B36D-4DF7-A76D-289212CFF394}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="666750" y="58737501"/>
-              <a:ext cx="10477500" cy="184149"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln w="19050">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="2">
-              <a:schemeClr val="accent1">
-                <a:shade val="15000"/>
-              </a:schemeClr>
-            </a:lnRef>
-            <a:fillRef idx="1">
-              <a:schemeClr val="accent1"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:schemeClr val="accent1"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="lt1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-              <a:prstTxWarp prst="textNoShape">
-                <a:avLst/>
-              </a:prstTxWarp>
-              <a:noAutofit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="37" name="正方形/長方形 36">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{80D41CF4-B063-4EB7-82E1-0AEA0EB99E3E}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="6813550" y="58108850"/>
-              <a:ext cx="2825750" cy="2349500"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln w="19050">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="2">
-              <a:schemeClr val="accent1">
-                <a:shade val="15000"/>
-              </a:schemeClr>
-            </a:lnRef>
-            <a:fillRef idx="1">
-              <a:schemeClr val="accent1"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:schemeClr val="accent1"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="lt1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-              <a:prstTxWarp prst="textNoShape">
-                <a:avLst/>
-              </a:prstTxWarp>
-              <a:noAutofit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </xdr:grpSp>
-      <xdr:cxnSp macro="">
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="42" name="コネクタ: カギ線 41">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DA5866D1-37D3-4DD7-9B8B-6D96EC5CA5DD}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvCxnSpPr>
-            <a:stCxn id="8" idx="3"/>
-            <a:endCxn id="35" idx="1"/>
-          </xdr:cNvCxnSpPr>
-        </xdr:nvCxnSpPr>
-        <xdr:spPr>
-          <a:xfrm flipH="1">
-            <a:off x="1165732" y="58503631"/>
-            <a:ext cx="10105518" cy="4517924"/>
-          </a:xfrm>
-          <a:prstGeom prst="bentConnector5">
-            <a:avLst>
-              <a:gd name="adj1" fmla="val -2254"/>
-              <a:gd name="adj2" fmla="val 48019"/>
-              <a:gd name="adj3" fmla="val 102254"/>
-            </a:avLst>
-          </a:prstGeom>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-            <a:tailEnd type="triangle"/>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:lnRef>
-          <a:fillRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="tx1"/>
-          </a:fontRef>
-        </xdr:style>
-      </xdr:cxnSp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>207</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>47</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>246</xdr:row>
-      <xdr:rowOff>104094</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="51" name="グループ化 50">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E7308B17-EBA6-445F-788C-D58C64FF7C42}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="463176" y="47938766"/>
-          <a:ext cx="10650071" cy="9136034"/>
-          <a:chOff x="469900" y="47320201"/>
-          <a:chExt cx="10801350" cy="9019493"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:grpSp>
-        <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="41" name="グループ化 40">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{988A3D55-D67B-D27D-2D7C-4FEB3419E9B1}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvGrpSpPr/>
-        </xdr:nvGrpSpPr>
-        <xdr:grpSpPr>
-          <a:xfrm>
-            <a:off x="469900" y="47320201"/>
-            <a:ext cx="10801350" cy="4078861"/>
-            <a:chOff x="469900" y="47777401"/>
-            <a:chExt cx="10801350" cy="4078861"/>
-          </a:xfrm>
-        </xdr:grpSpPr>
-        <xdr:pic>
-          <xdr:nvPicPr>
-            <xdr:cNvPr id="5" name="図 4">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5DF54FD7-B60A-969C-0E3B-9C1243B89823}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvPicPr>
-              <a:picLocks noChangeAspect="1"/>
-            </xdr:cNvPicPr>
-          </xdr:nvPicPr>
-          <xdr:blipFill>
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
-            <a:stretch>
-              <a:fillRect/>
-            </a:stretch>
-          </xdr:blipFill>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="469900" y="47777401"/>
-              <a:ext cx="10801350" cy="4078861"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-          </xdr:spPr>
-        </xdr:pic>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="11" name="正方形/長方形 10">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{30A54CE4-58EF-4C62-8B83-2A8CD065CF82}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="603250" y="49580801"/>
-              <a:ext cx="10477500" cy="184150"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln w="19050">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="2">
-              <a:schemeClr val="accent1">
-                <a:shade val="15000"/>
-              </a:schemeClr>
-            </a:lnRef>
-            <a:fillRef idx="1">
-              <a:schemeClr val="accent1"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:schemeClr val="accent1"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="lt1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-              <a:prstTxWarp prst="textNoShape">
-                <a:avLst/>
-              </a:prstTxWarp>
-              <a:noAutofit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="12" name="正方形/長方形 11">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CDF8CC91-32B9-49C8-8597-F2421EC29D22}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="5746750" y="48952150"/>
-              <a:ext cx="2508250" cy="2413000"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln w="19050">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="2">
-              <a:schemeClr val="accent1">
-                <a:shade val="15000"/>
-              </a:schemeClr>
-            </a:lnRef>
-            <a:fillRef idx="1">
-              <a:schemeClr val="accent1"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:schemeClr val="accent1"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="lt1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-              <a:prstTxWarp prst="textNoShape">
-                <a:avLst/>
-              </a:prstTxWarp>
-              <a:noAutofit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </xdr:grpSp>
-      <xdr:grpSp>
-        <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="40" name="グループ化 39">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{51BC9279-AB1E-FFA6-6FC5-AF565B8619D2}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvGrpSpPr/>
-        </xdr:nvGrpSpPr>
-        <xdr:grpSpPr>
-          <a:xfrm>
-            <a:off x="1399935" y="51659652"/>
-            <a:ext cx="8640322" cy="4680042"/>
-            <a:chOff x="477371" y="51944495"/>
-            <a:chExt cx="8641229" cy="4678228"/>
-          </a:xfrm>
-        </xdr:grpSpPr>
-        <xdr:pic>
-          <xdr:nvPicPr>
-            <xdr:cNvPr id="7" name="図 6">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2A6F7372-2F69-2E80-76D5-6DE42FDA1DD9}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvPicPr>
-              <a:picLocks noChangeAspect="1"/>
-            </xdr:cNvPicPr>
-          </xdr:nvPicPr>
-          <xdr:blipFill>
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
-            <a:stretch>
-              <a:fillRect/>
-            </a:stretch>
-          </xdr:blipFill>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="477371" y="51944495"/>
-              <a:ext cx="8641080" cy="4678228"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-          </xdr:spPr>
-        </xdr:pic>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="13" name="正方形/長方形 12">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD1FA312-4226-4198-BAF8-59AB9903FB28}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="673100" y="54032150"/>
-              <a:ext cx="7493000" cy="177800"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln w="19050">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="2">
-              <a:schemeClr val="accent1">
-                <a:shade val="15000"/>
-              </a:schemeClr>
-            </a:lnRef>
-            <a:fillRef idx="1">
-              <a:schemeClr val="accent1"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:schemeClr val="accent1"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="lt1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-              <a:prstTxWarp prst="textNoShape">
-                <a:avLst/>
-              </a:prstTxWarp>
-              <a:noAutofit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="31" name="正方形/長方形 30">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BA9B92BD-8EB6-4163-A986-0CE207707B1C}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="8166100" y="53301900"/>
-              <a:ext cx="952500" cy="2800350"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln w="19050">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="2">
-              <a:schemeClr val="accent1">
-                <a:shade val="15000"/>
-              </a:schemeClr>
-            </a:lnRef>
-            <a:fillRef idx="1">
-              <a:schemeClr val="accent1"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:schemeClr val="accent1"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="lt1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-              <a:prstTxWarp prst="textNoShape">
-                <a:avLst/>
-              </a:prstTxWarp>
-              <a:noAutofit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </xdr:grpSp>
-      <xdr:cxnSp macro="">
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="48" name="コネクタ: カギ線 47">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CE523132-F5A7-4E07-ADB2-F697B59E69EC}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvCxnSpPr>
-            <a:stCxn id="5" idx="3"/>
-            <a:endCxn id="7" idx="1"/>
-          </xdr:cNvCxnSpPr>
-        </xdr:nvCxnSpPr>
-        <xdr:spPr>
-          <a:xfrm flipH="1">
-            <a:off x="1399935" y="49358724"/>
-            <a:ext cx="9871315" cy="4641856"/>
-          </a:xfrm>
-          <a:prstGeom prst="bentConnector5">
-            <a:avLst>
-              <a:gd name="adj1" fmla="val -2307"/>
-              <a:gd name="adj2" fmla="val 46775"/>
-              <a:gd name="adj3" fmla="val 102307"/>
-            </a:avLst>
-          </a:prstGeom>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-            <a:tailEnd type="triangle"/>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:lnRef>
-          <a:fillRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="tx1"/>
-          </a:fontRef>
-        </xdr:style>
-      </xdr:cxnSp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>216647</xdr:colOff>
-      <xdr:row>298</xdr:row>
-      <xdr:rowOff>2</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>38</xdr:col>
-      <xdr:colOff>167938</xdr:colOff>
-      <xdr:row>333</xdr:row>
-      <xdr:rowOff>188258</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="55" name="グループ化 54">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9D1B27AD-17B9-DD1A-CD2F-98F7C86D327E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="448235" y="69013296"/>
-          <a:ext cx="8520056" cy="8293844"/>
-          <a:chOff x="686548" y="66530072"/>
-          <a:chExt cx="8644441" cy="8189255"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="52" name="図 51">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9163C4E2-B2D1-0F32-F9A2-E52C7E4CA1B0}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="686548" y="66530072"/>
-            <a:ext cx="8644441" cy="8189255"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-      </xdr:pic>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="53" name="正方形/長方形 52">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{101CBB97-6B96-4446-9AC0-08648FD81F3C}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="3666191" y="69288212"/>
-            <a:ext cx="2237441" cy="213658"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="54" name="正方形/長方形 53">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AAC4C119-8CFF-4114-B07B-E264C0AA8594}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="1756708" y="70483507"/>
-            <a:ext cx="835212" cy="265952"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>14942</xdr:colOff>
-      <xdr:row>338</xdr:row>
-      <xdr:rowOff>14942</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>48</xdr:col>
-      <xdr:colOff>11954</xdr:colOff>
-      <xdr:row>360</xdr:row>
-      <xdr:rowOff>194279</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="59" name="グループ化 58">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{841C02FC-192B-1562-1C51-B328CA71E9D3}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="478118" y="78291766"/>
-          <a:ext cx="10650071" cy="5274278"/>
-          <a:chOff x="469900" y="76581001"/>
-          <a:chExt cx="10801350" cy="5208537"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="56" name="図 55">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F813596-B97F-E712-D6F1-14E5ECC55B2C}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="469900" y="76581001"/>
-            <a:ext cx="10801350" cy="4525873"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-      </xdr:pic>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="57" name="吹き出し: 四角形 56">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A0A4239A-02B8-4279-BB5A-1CCF0AF47FF4}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="2894106" y="81197823"/>
-            <a:ext cx="2135496" cy="591715"/>
-          </a:xfrm>
-          <a:prstGeom prst="wedgeRectCallout">
-            <a:avLst>
-              <a:gd name="adj1" fmla="val -9330"/>
-              <a:gd name="adj2" fmla="val -105511"/>
-            </a:avLst>
-          </a:prstGeom>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent2"/>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="lt1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent2"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="dk1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:r>
-              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1000">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>contracts</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1000">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>の</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1000">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>3</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1000">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>件のデータ取り込みも成功しています。</a:t>
-            </a:r>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="58" name="正方形/長方形 57">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0FF688AF-79A2-4715-891C-3DFCADAAC11F}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="1704414" y="77746412"/>
-            <a:ext cx="2364442" cy="171824"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>368</xdr:row>
@@ -4182,7 +2191,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4225,8 +2234,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="478117" y="96579766"/>
-          <a:ext cx="10650071" cy="5873983"/>
+          <a:off x="484841" y="95333672"/>
+          <a:ext cx="10804712" cy="5799277"/>
           <a:chOff x="484841" y="95333672"/>
           <a:chExt cx="10804712" cy="5799277"/>
         </a:xfrm>
@@ -4245,7 +2254,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
@@ -4375,6 +2384,99 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>72339</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="9" name="グループ化 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B7DFC77C-D546-098A-0D70-C7B25898DDA4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="234950" y="1143000"/>
+          <a:ext cx="10801350" cy="7844739"/>
+          <a:chOff x="234950" y="1143000"/>
+          <a:chExt cx="10801350" cy="7844739"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="2" name="図 1">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BF017EE5-B97F-3076-DB92-D24445B2C55B}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="234950" y="1143000"/>
+            <a:ext cx="10801350" cy="7844739"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="3" name="図 2">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07DDD2F5-A401-45AE-BCE1-B5AC9979943C}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="264833" y="1165413"/>
+            <a:ext cx="252071" cy="225939"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>14941</xdr:colOff>
       <xdr:row>47</xdr:row>
@@ -4386,35 +2488,2432 @@
       <xdr:row>75</xdr:row>
       <xdr:rowOff>123629</xdr:rowOff>
     </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="34" name="図 33">
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="44" name="グループ化 43">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B678E0AC-466B-6F6A-86A5-AF148E082DD0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B8DBD2EF-125E-4602-C7F7-A891A1C20562}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="478117" y="10899589"/>
-          <a:ext cx="10650071" cy="6593158"/>
+          <a:off x="484841" y="10759142"/>
+          <a:ext cx="10804712" cy="6509487"/>
+          <a:chOff x="484841" y="10759142"/>
+          <a:chExt cx="10804712" cy="6509487"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="34" name="図 33">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B678E0AC-466B-6F6A-86A5-AF148E082DD0}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="484841" y="10759142"/>
+            <a:ext cx="10804712" cy="6509487"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="43" name="図 42">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1C7F2C3F-0093-4AD2-8CFE-00AC276FD002}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="499782" y="10789024"/>
+            <a:ext cx="252070" cy="225939"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>48</xdr:col>
+      <xdr:colOff>4482</xdr:colOff>
+      <xdr:row>120</xdr:row>
+      <xdr:rowOff>63948</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="49" name="グループ化 48">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7F7C4010-5352-5923-C2CC-1C60B1049E03}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="469900" y="19888200"/>
+          <a:ext cx="10812182" cy="7607748"/>
+          <a:chOff x="469900" y="19888200"/>
+          <a:chExt cx="10812182" cy="7607748"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="28" name="グループ化 27">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E22C8FD6-F62C-B794-452E-D1BFD4FC1830}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="469900" y="19888200"/>
+            <a:ext cx="10812182" cy="7607748"/>
+            <a:chOff x="469900" y="19659600"/>
+            <a:chExt cx="10812182" cy="7607748"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:grpSp>
+          <xdr:nvGrpSpPr>
+            <xdr:cNvPr id="26" name="グループ化 25">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AEBCB02B-1EB2-0D46-734B-5FDBF27841FC}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGrpSpPr/>
+          </xdr:nvGrpSpPr>
+          <xdr:grpSpPr>
+            <a:xfrm>
+              <a:off x="469900" y="19659600"/>
+              <a:ext cx="10801350" cy="3631672"/>
+              <a:chOff x="469900" y="24231600"/>
+              <a:chExt cx="10801350" cy="3631673"/>
+            </a:xfrm>
+          </xdr:grpSpPr>
+          <xdr:pic>
+            <xdr:nvPicPr>
+              <xdr:cNvPr id="22" name="図 21">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{58677F60-D64E-96C7-5976-08643B1BE810}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvPicPr>
+                <a:picLocks noChangeAspect="1"/>
+              </xdr:cNvPicPr>
+            </xdr:nvPicPr>
+            <xdr:blipFill>
+              <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+              <a:stretch>
+                <a:fillRect/>
+              </a:stretch>
+            </xdr:blipFill>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="469900" y="24231600"/>
+                <a:ext cx="10801350" cy="3631673"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+            </xdr:spPr>
+          </xdr:pic>
+          <xdr:sp macro="" textlink="">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="14" name="正方形/長方形 13">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C15181F7-3FF8-439F-B980-ECADE959571F}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvSpPr/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="1756708" y="25591247"/>
+                <a:ext cx="1409701" cy="1274482"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="2">
+                <a:schemeClr val="accent1">
+                  <a:shade val="15000"/>
+                </a:schemeClr>
+              </a:lnRef>
+              <a:fillRef idx="1">
+                <a:schemeClr val="accent1"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:schemeClr val="accent1"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="lt1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+                <a:prstTxWarp prst="textNoShape">
+                  <a:avLst/>
+                </a:prstTxWarp>
+                <a:noAutofit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+          <xdr:sp macro="" textlink="">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="23" name="正方形/長方形 22">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E279C728-F6A2-4081-9D5F-E782D2AA1805}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvSpPr/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="611841" y="26517600"/>
+                <a:ext cx="850154" cy="340658"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="2">
+                <a:schemeClr val="accent1">
+                  <a:shade val="15000"/>
+                </a:schemeClr>
+              </a:lnRef>
+              <a:fillRef idx="1">
+                <a:schemeClr val="accent1"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:schemeClr val="accent1"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="lt1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+                <a:prstTxWarp prst="textNoShape">
+                  <a:avLst/>
+                </a:prstTxWarp>
+                <a:noAutofit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+        </xdr:grpSp>
+        <xdr:grpSp>
+          <xdr:nvGrpSpPr>
+            <xdr:cNvPr id="27" name="グループ化 26">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DAFB44ED-67DE-E8E2-A8B0-B9163D3A8CDC}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGrpSpPr/>
+          </xdr:nvGrpSpPr>
+          <xdr:grpSpPr>
+            <a:xfrm>
+              <a:off x="477370" y="23481554"/>
+              <a:ext cx="10804712" cy="3785794"/>
+              <a:chOff x="477370" y="28053554"/>
+              <a:chExt cx="10804712" cy="3785794"/>
+            </a:xfrm>
+          </xdr:grpSpPr>
+          <xdr:pic>
+            <xdr:nvPicPr>
+              <xdr:cNvPr id="21" name="図 20">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E49F11E9-615B-0003-A94F-A557E2E579B2}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvPicPr>
+                <a:picLocks noChangeAspect="1"/>
+              </xdr:cNvPicPr>
+            </xdr:nvPicPr>
+            <xdr:blipFill>
+              <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+              <a:stretch>
+                <a:fillRect/>
+              </a:stretch>
+            </xdr:blipFill>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="477370" y="28053554"/>
+                <a:ext cx="10804712" cy="3785794"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+            </xdr:spPr>
+          </xdr:pic>
+          <xdr:sp macro="" textlink="">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="24" name="正方形/長方形 23">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5E4BEC83-F88E-4F71-BF7F-BA6DEADB2F35}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvSpPr/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="3233643" y="29440094"/>
+                <a:ext cx="1159810" cy="1371600"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="2">
+                <a:schemeClr val="accent1">
+                  <a:shade val="15000"/>
+                </a:schemeClr>
+              </a:lnRef>
+              <a:fillRef idx="1">
+                <a:schemeClr val="accent1"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:schemeClr val="accent1"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="lt1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+                <a:prstTxWarp prst="textNoShape">
+                  <a:avLst/>
+                </a:prstTxWarp>
+                <a:noAutofit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+          <xdr:sp macro="" textlink="">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="25" name="正方形/長方形 24">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C21E088F-C003-492C-BC9A-D4F95436DB52}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvSpPr/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="704850" y="30361965"/>
+                <a:ext cx="846793" cy="337670"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="2">
+                <a:schemeClr val="accent1">
+                  <a:shade val="15000"/>
+                </a:schemeClr>
+              </a:lnRef>
+              <a:fillRef idx="1">
+                <a:schemeClr val="accent1"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:schemeClr val="accent1"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="lt1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+                <a:prstTxWarp prst="textNoShape">
+                  <a:avLst/>
+                </a:prstTxWarp>
+                <a:noAutofit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+        </xdr:grpSp>
+      </xdr:grpSp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="45" name="図 44">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FD5E2CE1-6C4D-F717-036F-06721BBA4745}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="5245100" y="21005800"/>
+            <a:ext cx="2178050" cy="136943"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="47" name="図 46">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9AB3C716-E345-CE77-2805-257C759EB750}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="5346700" y="24822150"/>
+            <a:ext cx="2178050" cy="136943"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>226785</xdr:colOff>
+      <xdr:row>156</xdr:row>
+      <xdr:rowOff>18143</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>47</xdr:col>
+      <xdr:colOff>223797</xdr:colOff>
+      <xdr:row>199</xdr:row>
+      <xdr:rowOff>71593</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="78" name="グループ化 77">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4C31975A-1AA6-99F3-6A97-DBF745D9D909}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="461735" y="35679743"/>
+          <a:ext cx="10804712" cy="9883250"/>
+          <a:chOff x="461735" y="35679743"/>
+          <a:chExt cx="10804712" cy="9883250"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="4" name="グループ化 3">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E23210DE-EE71-0266-E784-864445BD622B}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="461735" y="35679743"/>
+            <a:ext cx="10804712" cy="9883250"/>
+            <a:chOff x="461735" y="35679743"/>
+            <a:chExt cx="10804712" cy="9883250"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:grpSp>
+          <xdr:nvGrpSpPr>
+            <xdr:cNvPr id="20" name="グループ化 19">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A1DF8CDD-7427-FFCA-3E88-F832DEB0588D}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGrpSpPr/>
+          </xdr:nvGrpSpPr>
+          <xdr:grpSpPr>
+            <a:xfrm>
+              <a:off x="461735" y="35679743"/>
+              <a:ext cx="10800443" cy="4848180"/>
+              <a:chOff x="469900" y="31318200"/>
+              <a:chExt cx="10801350" cy="4848180"/>
+            </a:xfrm>
+          </xdr:grpSpPr>
+          <xdr:pic>
+            <xdr:nvPicPr>
+              <xdr:cNvPr id="15" name="図 14">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4BC7F28C-E706-A061-0DD2-0D51A2323C1E}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvPicPr>
+                <a:picLocks noChangeAspect="1"/>
+              </xdr:cNvPicPr>
+            </xdr:nvPicPr>
+            <xdr:blipFill>
+              <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+              <a:stretch>
+                <a:fillRect/>
+              </a:stretch>
+            </xdr:blipFill>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="469900" y="31318200"/>
+                <a:ext cx="10801350" cy="4848180"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+            </xdr:spPr>
+          </xdr:pic>
+          <xdr:sp macro="" textlink="">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="16" name="正方形/長方形 15">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{99B056D6-F636-48D8-8E18-6030070FD15D}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvSpPr/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="1667062" y="34049447"/>
+                <a:ext cx="9435353" cy="1405965"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="2">
+                <a:schemeClr val="accent1">
+                  <a:shade val="15000"/>
+                </a:schemeClr>
+              </a:lnRef>
+              <a:fillRef idx="1">
+                <a:schemeClr val="accent1"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:schemeClr val="accent1"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="lt1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+                <a:prstTxWarp prst="textNoShape">
+                  <a:avLst/>
+                </a:prstTxWarp>
+                <a:noAutofit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+        </xdr:grpSp>
+        <xdr:grpSp>
+          <xdr:nvGrpSpPr>
+            <xdr:cNvPr id="19" name="グループ化 18">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{685B3851-9BB5-3E8A-FE75-B0460732DAE0}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGrpSpPr/>
+          </xdr:nvGrpSpPr>
+          <xdr:grpSpPr>
+            <a:xfrm>
+              <a:off x="461735" y="40714814"/>
+              <a:ext cx="10804712" cy="4848179"/>
+              <a:chOff x="469900" y="36576000"/>
+              <a:chExt cx="10801350" cy="4848180"/>
+            </a:xfrm>
+          </xdr:grpSpPr>
+          <xdr:pic>
+            <xdr:nvPicPr>
+              <xdr:cNvPr id="17" name="図 16">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C19CE300-BC63-35F7-C7D7-2EAD130389D9}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvPicPr>
+                <a:picLocks noChangeAspect="1"/>
+              </xdr:cNvPicPr>
+            </xdr:nvPicPr>
+            <xdr:blipFill>
+              <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+              <a:stretch>
+                <a:fillRect/>
+              </a:stretch>
+            </xdr:blipFill>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="469900" y="36576000"/>
+                <a:ext cx="10801350" cy="4848180"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+            </xdr:spPr>
+          </xdr:pic>
+          <xdr:sp macro="" textlink="">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="18" name="正方形/長方形 17">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F903AE1-B6F0-4384-A5C7-C216727251B8}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvSpPr/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="1652120" y="39334142"/>
+                <a:ext cx="9435353" cy="1408952"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="2">
+                <a:schemeClr val="accent1">
+                  <a:shade val="15000"/>
+                </a:schemeClr>
+              </a:lnRef>
+              <a:fillRef idx="1">
+                <a:schemeClr val="accent1"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:schemeClr val="accent1"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="lt1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+                <a:prstTxWarp prst="textNoShape">
+                  <a:avLst/>
+                </a:prstTxWarp>
+                <a:noAutofit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+        </xdr:grpSp>
+      </xdr:grpSp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="76" name="図 75">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A690C992-092A-4948-8658-658DDCF9B5EC}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="4946650" y="36790922"/>
+            <a:ext cx="2091592" cy="130550"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="77" name="図 76">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{83ED1BE8-9985-4652-BB6C-3643479AC66E}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="5203090" y="41825007"/>
+            <a:ext cx="2349502" cy="146737"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>207</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>47</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>246</xdr:row>
+      <xdr:rowOff>104094</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="80" name="グループ化 79">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{667723A2-EF3C-553D-AE98-EFF6CB08F173}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="469900" y="47320201"/>
+          <a:ext cx="10801350" cy="9019493"/>
+          <a:chOff x="469900" y="47320201"/>
+          <a:chExt cx="10801350" cy="9019493"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="51" name="グループ化 50">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E7308B17-EBA6-445F-788C-D58C64FF7C42}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="469900" y="47320201"/>
+            <a:ext cx="10801350" cy="9019493"/>
+            <a:chOff x="469900" y="47320201"/>
+            <a:chExt cx="10801350" cy="9019493"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:grpSp>
+          <xdr:nvGrpSpPr>
+            <xdr:cNvPr id="41" name="グループ化 40">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{988A3D55-D67B-D27D-2D7C-4FEB3419E9B1}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGrpSpPr/>
+          </xdr:nvGrpSpPr>
+          <xdr:grpSpPr>
+            <a:xfrm>
+              <a:off x="469900" y="47320201"/>
+              <a:ext cx="10801350" cy="4078861"/>
+              <a:chOff x="469900" y="47777401"/>
+              <a:chExt cx="10801350" cy="4078861"/>
+            </a:xfrm>
+          </xdr:grpSpPr>
+          <xdr:pic>
+            <xdr:nvPicPr>
+              <xdr:cNvPr id="5" name="図 4">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5DF54FD7-B60A-969C-0E3B-9C1243B89823}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvPicPr>
+                <a:picLocks noChangeAspect="1"/>
+              </xdr:cNvPicPr>
+            </xdr:nvPicPr>
+            <xdr:blipFill>
+              <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+              <a:stretch>
+                <a:fillRect/>
+              </a:stretch>
+            </xdr:blipFill>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="469900" y="47777401"/>
+                <a:ext cx="10801350" cy="4078861"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+            </xdr:spPr>
+          </xdr:pic>
+          <xdr:sp macro="" textlink="">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="11" name="正方形/長方形 10">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{30A54CE4-58EF-4C62-8B83-2A8CD065CF82}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvSpPr/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="603250" y="49580801"/>
+                <a:ext cx="10477500" cy="184150"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="2">
+                <a:schemeClr val="accent1">
+                  <a:shade val="15000"/>
+                </a:schemeClr>
+              </a:lnRef>
+              <a:fillRef idx="1">
+                <a:schemeClr val="accent1"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:schemeClr val="accent1"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="lt1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+                <a:prstTxWarp prst="textNoShape">
+                  <a:avLst/>
+                </a:prstTxWarp>
+                <a:noAutofit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+          <xdr:sp macro="" textlink="">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="12" name="正方形/長方形 11">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CDF8CC91-32B9-49C8-8597-F2421EC29D22}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvSpPr/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="5746750" y="48952150"/>
+                <a:ext cx="2508250" cy="2413000"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="2">
+                <a:schemeClr val="accent1">
+                  <a:shade val="15000"/>
+                </a:schemeClr>
+              </a:lnRef>
+              <a:fillRef idx="1">
+                <a:schemeClr val="accent1"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:schemeClr val="accent1"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="lt1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+                <a:prstTxWarp prst="textNoShape">
+                  <a:avLst/>
+                </a:prstTxWarp>
+                <a:noAutofit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+        </xdr:grpSp>
+        <xdr:grpSp>
+          <xdr:nvGrpSpPr>
+            <xdr:cNvPr id="40" name="グループ化 39">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{51BC9279-AB1E-FFA6-6FC5-AF565B8619D2}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGrpSpPr/>
+          </xdr:nvGrpSpPr>
+          <xdr:grpSpPr>
+            <a:xfrm>
+              <a:off x="1399935" y="51659652"/>
+              <a:ext cx="8640322" cy="4680042"/>
+              <a:chOff x="477371" y="51944495"/>
+              <a:chExt cx="8641229" cy="4678228"/>
+            </a:xfrm>
+          </xdr:grpSpPr>
+          <xdr:pic>
+            <xdr:nvPicPr>
+              <xdr:cNvPr id="7" name="図 6">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2A6F7372-2F69-2E80-76D5-6DE42FDA1DD9}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvPicPr>
+                <a:picLocks noChangeAspect="1"/>
+              </xdr:cNvPicPr>
+            </xdr:nvPicPr>
+            <xdr:blipFill>
+              <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+              <a:stretch>
+                <a:fillRect/>
+              </a:stretch>
+            </xdr:blipFill>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="477371" y="51944495"/>
+                <a:ext cx="8641080" cy="4678228"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+            </xdr:spPr>
+          </xdr:pic>
+          <xdr:sp macro="" textlink="">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="13" name="正方形/長方形 12">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD1FA312-4226-4198-BAF8-59AB9903FB28}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvSpPr/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="673100" y="54032150"/>
+                <a:ext cx="7493000" cy="177800"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="2">
+                <a:schemeClr val="accent1">
+                  <a:shade val="15000"/>
+                </a:schemeClr>
+              </a:lnRef>
+              <a:fillRef idx="1">
+                <a:schemeClr val="accent1"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:schemeClr val="accent1"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="lt1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+                <a:prstTxWarp prst="textNoShape">
+                  <a:avLst/>
+                </a:prstTxWarp>
+                <a:noAutofit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+          <xdr:sp macro="" textlink="">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="31" name="正方形/長方形 30">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BA9B92BD-8EB6-4163-A986-0CE207707B1C}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvSpPr/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="8166100" y="53301900"/>
+                <a:ext cx="952500" cy="2800350"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="2">
+                <a:schemeClr val="accent1">
+                  <a:shade val="15000"/>
+                </a:schemeClr>
+              </a:lnRef>
+              <a:fillRef idx="1">
+                <a:schemeClr val="accent1"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:schemeClr val="accent1"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="lt1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+                <a:prstTxWarp prst="textNoShape">
+                  <a:avLst/>
+                </a:prstTxWarp>
+                <a:noAutofit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+        </xdr:grpSp>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="48" name="コネクタ: カギ線 47">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CE523132-F5A7-4E07-ADB2-F697B59E69EC}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr>
+              <a:stCxn id="5" idx="3"/>
+              <a:endCxn id="7" idx="1"/>
+            </xdr:cNvCxnSpPr>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm flipH="1">
+              <a:off x="1399935" y="49358724"/>
+              <a:ext cx="9871315" cy="4641856"/>
+            </a:xfrm>
+            <a:prstGeom prst="bentConnector5">
+              <a:avLst>
+                <a:gd name="adj1" fmla="val -2307"/>
+                <a:gd name="adj2" fmla="val 46775"/>
+                <a:gd name="adj3" fmla="val 102307"/>
+              </a:avLst>
+            </a:prstGeom>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:tailEnd type="triangle"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+      </xdr:grpSp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="79" name="図 78">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5B7726A3-D3DF-4B15-9A47-1BF18E788911}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="4276509" y="48269366"/>
+            <a:ext cx="1797510" cy="114465"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>10139</xdr:colOff>
+      <xdr:row>252</xdr:row>
+      <xdr:rowOff>195835</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>48</xdr:col>
+      <xdr:colOff>2882</xdr:colOff>
+      <xdr:row>291</xdr:row>
+      <xdr:rowOff>53241</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="82" name="グループ化 81">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D60C67C0-7B2E-4DEB-AC4B-B9D507E8C153}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="480039" y="57803035"/>
+          <a:ext cx="10800443" cy="8772806"/>
+          <a:chOff x="480039" y="57803035"/>
+          <a:chExt cx="10800443" cy="8772806"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="46" name="グループ化 45">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8842D565-9281-EE18-CAFA-88240E689EAB}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="480039" y="57803035"/>
+            <a:ext cx="10800443" cy="8772806"/>
+            <a:chOff x="469900" y="56464200"/>
+            <a:chExt cx="10801350" cy="8775793"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:grpSp>
+          <xdr:nvGrpSpPr>
+            <xdr:cNvPr id="39" name="グループ化 38">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{86ED658B-30DD-AF28-1045-B5E23B9C9DD4}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGrpSpPr/>
+          </xdr:nvGrpSpPr>
+          <xdr:grpSpPr>
+            <a:xfrm>
+              <a:off x="1098550" y="60803117"/>
+              <a:ext cx="8708263" cy="4436876"/>
+              <a:chOff x="628650" y="61264800"/>
+              <a:chExt cx="8708262" cy="4439864"/>
+            </a:xfrm>
+          </xdr:grpSpPr>
+          <xdr:pic>
+            <xdr:nvPicPr>
+              <xdr:cNvPr id="35" name="図 34">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0AE4A581-2C8F-F989-CA65-1EAFBC27C359}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvPicPr>
+                <a:picLocks noChangeAspect="1"/>
+              </xdr:cNvPicPr>
+            </xdr:nvPicPr>
+            <xdr:blipFill>
+              <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+              <a:stretch>
+                <a:fillRect/>
+              </a:stretch>
+            </xdr:blipFill>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="695832" y="61264800"/>
+                <a:ext cx="8641080" cy="4439864"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+            </xdr:spPr>
+          </xdr:pic>
+          <xdr:sp macro="" textlink="">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="32" name="正方形/長方形 31">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{408A2820-2DB6-4AA8-88B4-D47DD642983F}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvSpPr/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="628650" y="63303150"/>
+                <a:ext cx="7334250" cy="184150"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="2">
+                <a:schemeClr val="accent1">
+                  <a:shade val="15000"/>
+                </a:schemeClr>
+              </a:lnRef>
+              <a:fillRef idx="1">
+                <a:schemeClr val="accent1"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:schemeClr val="accent1"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="lt1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+                <a:prstTxWarp prst="textNoShape">
+                  <a:avLst/>
+                </a:prstTxWarp>
+                <a:noAutofit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+          <xdr:sp macro="" textlink="">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="33" name="正方形/長方形 32">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{55C9EF02-38AC-49EA-B3E7-6574CCEFF4B5}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvSpPr/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="7956550" y="62591950"/>
+                <a:ext cx="1143000" cy="2470150"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="2">
+                <a:schemeClr val="accent1">
+                  <a:shade val="15000"/>
+                </a:schemeClr>
+              </a:lnRef>
+              <a:fillRef idx="1">
+                <a:schemeClr val="accent1"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:schemeClr val="accent1"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="lt1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+                <a:prstTxWarp prst="textNoShape">
+                  <a:avLst/>
+                </a:prstTxWarp>
+                <a:noAutofit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+        </xdr:grpSp>
+        <xdr:grpSp>
+          <xdr:nvGrpSpPr>
+            <xdr:cNvPr id="38" name="グループ化 37">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D139E68B-8315-CF5B-0C07-8E4B748BFBA5}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGrpSpPr/>
+          </xdr:nvGrpSpPr>
+          <xdr:grpSpPr>
+            <a:xfrm>
+              <a:off x="469900" y="56464200"/>
+              <a:ext cx="10801350" cy="4078861"/>
+              <a:chOff x="469900" y="56921400"/>
+              <a:chExt cx="10801350" cy="4078861"/>
+            </a:xfrm>
+          </xdr:grpSpPr>
+          <xdr:pic>
+            <xdr:nvPicPr>
+              <xdr:cNvPr id="8" name="図 7">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3BD021D8-7293-67D3-F400-8BCFE7E6B04F}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvPicPr>
+                <a:picLocks noChangeAspect="1"/>
+              </xdr:cNvPicPr>
+            </xdr:nvPicPr>
+            <xdr:blipFill>
+              <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
+              <a:stretch>
+                <a:fillRect/>
+              </a:stretch>
+            </xdr:blipFill>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="469900" y="56921400"/>
+                <a:ext cx="10801350" cy="4078861"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+            </xdr:spPr>
+          </xdr:pic>
+          <xdr:sp macro="" textlink="">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="36" name="正方形/長方形 35">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D8EF5C6-B36D-4DF7-A76D-289212CFF394}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvSpPr/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="666750" y="58737501"/>
+                <a:ext cx="10477500" cy="184149"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="2">
+                <a:schemeClr val="accent1">
+                  <a:shade val="15000"/>
+                </a:schemeClr>
+              </a:lnRef>
+              <a:fillRef idx="1">
+                <a:schemeClr val="accent1"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:schemeClr val="accent1"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="lt1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+                <a:prstTxWarp prst="textNoShape">
+                  <a:avLst/>
+                </a:prstTxWarp>
+                <a:noAutofit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+          <xdr:sp macro="" textlink="">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="37" name="正方形/長方形 36">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{80D41CF4-B063-4EB7-82E1-0AEA0EB99E3E}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvSpPr/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="6813550" y="58108850"/>
+                <a:ext cx="2825750" cy="2349500"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="2">
+                <a:schemeClr val="accent1">
+                  <a:shade val="15000"/>
+                </a:schemeClr>
+              </a:lnRef>
+              <a:fillRef idx="1">
+                <a:schemeClr val="accent1"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:schemeClr val="accent1"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="lt1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+                <a:prstTxWarp prst="textNoShape">
+                  <a:avLst/>
+                </a:prstTxWarp>
+                <a:noAutofit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+        </xdr:grpSp>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="42" name="コネクタ: カギ線 41">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DA5866D1-37D3-4DD7-9B8B-6D96EC5CA5DD}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr>
+              <a:stCxn id="8" idx="3"/>
+              <a:endCxn id="35" idx="1"/>
+            </xdr:cNvCxnSpPr>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm flipH="1">
+              <a:off x="1165732" y="58503631"/>
+              <a:ext cx="10105518" cy="4517924"/>
+            </a:xfrm>
+            <a:prstGeom prst="bentConnector5">
+              <a:avLst>
+                <a:gd name="adj1" fmla="val -2254"/>
+                <a:gd name="adj2" fmla="val 48019"/>
+                <a:gd name="adj3" fmla="val 102254"/>
+              </a:avLst>
+            </a:prstGeom>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:tailEnd type="triangle"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+      </xdr:grpSp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="81" name="図 80">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BA853B67-F682-459F-84F5-57761F2B0165}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="4508873" y="58745717"/>
+            <a:ext cx="2024664" cy="127513"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>14942</xdr:colOff>
+      <xdr:row>338</xdr:row>
+      <xdr:rowOff>14942</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>48</xdr:col>
+      <xdr:colOff>11954</xdr:colOff>
+      <xdr:row>360</xdr:row>
+      <xdr:rowOff>194279</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="84" name="グループ化 83">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AE0E688B-0B29-DC8B-CD2D-6B9600AEDD26}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="484842" y="77281742"/>
+          <a:ext cx="10804712" cy="5208537"/>
+          <a:chOff x="484842" y="77281742"/>
+          <a:chExt cx="10804712" cy="5208537"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="59" name="グループ化 58">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{841C02FC-192B-1562-1C51-B328CA71E9D3}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="484842" y="77281742"/>
+            <a:ext cx="10804712" cy="5208537"/>
+            <a:chOff x="469900" y="76581001"/>
+            <a:chExt cx="10801350" cy="5208537"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="56" name="図 55">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F813596-B97F-E712-D6F1-14E5ECC55B2C}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="469900" y="76581001"/>
+              <a:ext cx="10801350" cy="4525873"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="57" name="吹き出し: 四角形 56">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A0A4239A-02B8-4279-BB5A-1CCF0AF47FF4}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2894106" y="81197823"/>
+              <a:ext cx="2135496" cy="591715"/>
+            </a:xfrm>
+            <a:prstGeom prst="wedgeRectCallout">
+              <a:avLst>
+                <a:gd name="adj1" fmla="val -9330"/>
+                <a:gd name="adj2" fmla="val -105511"/>
+              </a:avLst>
+            </a:prstGeom>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent2"/>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="lt1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent2"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1000">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>contracts</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1000">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>の</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1000">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>3</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1000">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>件のデータ取り込みも成功しています。</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="58" name="正方形/長方形 57">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0FF688AF-79A2-4715-891C-3DFCADAAC11F}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="1704414" y="77746412"/>
+              <a:ext cx="2364442" cy="171824"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="83" name="図 82">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{290D464B-87A2-489C-BA6F-41C406D30E2C}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="4673600" y="78312142"/>
+            <a:ext cx="1913759" cy="128314"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>226785</xdr:colOff>
+      <xdr:row>129</xdr:row>
+      <xdr:rowOff>27215</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>38</xdr:col>
+      <xdr:colOff>173808</xdr:colOff>
+      <xdr:row>150</xdr:row>
+      <xdr:rowOff>57163</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="86" name="グループ化 85">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BA46CC27-86F7-4416-2712-2C6E6DD6D289}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="461735" y="29516615"/>
+          <a:ext cx="8640173" cy="4830548"/>
+          <a:chOff x="461735" y="29516615"/>
+          <a:chExt cx="8640173" cy="4830548"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="30" name="グループ化 29">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F6C50B54-12E5-EAC0-A0F4-7BB9D491C809}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="461735" y="29516615"/>
+            <a:ext cx="8640173" cy="4830548"/>
+            <a:chOff x="469900" y="28647572"/>
+            <a:chExt cx="8641080" cy="4830548"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="29" name="図 28">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7F9142CE-7E89-2A9A-A46E-8D7835D7ADF8}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="469900" y="28647572"/>
+              <a:ext cx="8641080" cy="4830548"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="6" name="正方形/長方形 5">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D80B9066-FBD9-44C5-85D2-CD32E326E1B9}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="612347" y="32618136"/>
+              <a:ext cx="3553958" cy="258012"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="10" name="正方形/長方形 9">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DEE2C7AD-4FE5-6E6F-45D0-AD49149A9DD0}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5295966" y="31881122"/>
+              <a:ext cx="2674225" cy="832125"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="85" name="図 84">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{03E66FD0-2EB2-4476-81B6-EED05977B3D9}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="508000" y="29571950"/>
+            <a:ext cx="248709" cy="228927"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>216647</xdr:colOff>
+      <xdr:row>298</xdr:row>
+      <xdr:rowOff>2</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>38</xdr:col>
+      <xdr:colOff>167938</xdr:colOff>
+      <xdr:row>333</xdr:row>
+      <xdr:rowOff>188258</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="88" name="グループ化 87">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{74F82326-9817-9681-C962-002ED5DAF530}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="451597" y="68122802"/>
+          <a:ext cx="8644441" cy="8189256"/>
+          <a:chOff x="451597" y="68122802"/>
+          <a:chExt cx="8644441" cy="8189256"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="55" name="グループ化 54">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9D1B27AD-17B9-DD1A-CD2F-98F7C86D327E}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="451597" y="68122802"/>
+            <a:ext cx="8644441" cy="8189256"/>
+            <a:chOff x="686548" y="66530072"/>
+            <a:chExt cx="8644441" cy="8189255"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="52" name="図 51">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9163C4E2-B2D1-0F32-F9A2-E52C7E4CA1B0}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="686548" y="66530072"/>
+              <a:ext cx="8644441" cy="8189255"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="53" name="正方形/長方形 52">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{101CBB97-6B96-4446-9AC0-08648FD81F3C}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3666191" y="69288212"/>
+              <a:ext cx="2237441" cy="213658"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="54" name="正方形/長方形 53">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AAC4C119-8CFF-4114-B07B-E264C0AA8594}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="1756708" y="70483507"/>
+              <a:ext cx="835212" cy="265952"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="87" name="図 86">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{17BFB384-7B71-4E80-8D84-E82A6E985283}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="469900" y="68148200"/>
+            <a:ext cx="248709" cy="228927"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
